--- a/songs/ILoveItIntro_v1/quelle/struktur.xlsx
+++ b/songs/ILoveItIntro_v1/quelle/struktur.xlsx
@@ -576,9 +576,9 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>progBlack(21175, 5)
-LAMPE1: progLampFireBurst(21175, 5, 18350, 1000)
-LAMPE2: progLampFireBurst(21175, 5, 19250, 1000)
+          <t>progBlack(21175, 3)
+LAMPE1: progLampFireBurst(21175, 3, 18350, 1000)
+LAMPE2: progLampFireBurst(21175, 3, 19250, 1000)
 Ausgabe: Blinder bei Takt 4 = 5250 ms, 500 ms lang, Blinder blendet 0 ms ein, 150 ms voll, 350 ms aus, Blinder bei Takt 5 = 7250 ms, 500 ms lang, Blinder blendet 0 ms ein, 150 ms voll, 350 ms aus, Blinder bei Takt 6 = 9250 ms, 500 ms lang, Blinder blendet 0 ms ein, 150 ms voll, 350 ms aus, Blinder bei Takt 7 = 11250 ms, 4000 ms lang, Blinder blendet 0 ms ein, 150 ms voll, 3850 ms aus
 Alles dunkel, der Einspieler läuft. Kurze Blinder auf die 1 von Takt 4, 5 und 6, auf Takt 7 einer, der lang über 2 Takte ausklingt; am Ende ein Feuer-Impuls auf Lampe 1 und gleich danach auf Lampe 2.</t>
         </is>
@@ -1150,10 +1150,10 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>progBlack(23400, 10)
-matrix: progScrollText("Nerds on Fire", 23400, 90, getRandomColor(), 10)
-LAMPE1: progLampFireBursts(23400, 10, 1000, 1175, 9175, 13175, 17175, 21175)
-LAMPE2: progLampFireBursts(23400, 10, 1000, 5175, 10075, 14075, 18075, 22075)
+          <t>progBlack(23400, 4)
+matrix: progScrollText("Nerds on Fire", 23400, 90, getRandomColor(), 4)
+LAMPE1: progLampFireBursts(23400, 4, 1000, 1175, 9175, 13175, 17175, 21175)
+LAMPE2: progLampFireBursts(23400, 4, 1000, 5175, 10075, 14075, 18075, 22075)
 Ausgabe: Blinder bei Takt 13 = 2075 ms, 500 ms lang, Blinder blendet 0 ms ein, 150 ms voll, 350 ms aus, Blinder bei Takt 15 = 6075 ms, 500 ms lang, Blinder blendet 0 ms ein, 150 ms voll, 350 ms aus
 Nur die Matrix zeigt den Lauftext "Nerds on Fire" (wie bisher), die Gitarren sind dunkel. Kurze Blinder auf die 1 von Takt 13 und 15. Ab Takt 12,5 springen Feuer-Impulse zwischen Lampe 1 und Lampe 2 hin und her (zehn Stück bis Takt 23).</t>
         </is>
@@ -1797,9 +1797,9 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>progBlack(21175, 15)
-LAMPE1: progLampFireBursts(21175, 15, 1000, 1775, 5775, 9775, 13775, 17775)
-LAMPE2: progLampFireBursts(21175, 15, 1000, 2675, 6675, 10675, 14675)
+          <t>progBlack(21175, 5)
+LAMPE1: progLampFireBursts(21175, 5, 1000, 1775, 5775, 9775, 13775, 17775)
+LAMPE2: progLampFireBursts(21175, 5, 1000, 2675, 6675, 10675, 14675)
 Ebene matrix: progWaterRipple (add, ab 6675 ms, baut sich 1000 ms auf)
 Ausgabe: Blinder bei Takt 33 = 18675 ms, 3000 ms lang, Blinder blendet 0 ms ein, 150 ms voll, 2850 ms aus
 Gitarren dunkel. Die Feuer-Impulse springen weiter zwischen Lampe 1 und Lampe 2 hin und her (neun Stück, Takt 24,5 bis 32,5). Ab Takt 27 laufen auf der Matrix Wasserwellen. Ein Blinder auf die 1 von Takt 33, der lang über 1,5 Takte ausklingt.</t>
@@ -2404,17 +2404,17 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>progBlack(5500, 20)
-matrix: progWaterRipple(5500, 20, 50, true, false)
-LAMPE1: progLampFireBurst(5500, 20, 1500, 1000)
-LAMPE2: progLampFireBursts(5500, 20, 1000, 600, 4600)
+          <t>progBlack(5500, 6)
+matrix: progWaterRipple(5500, 6, 50, true, false)
+LAMPE1: progLampFireBurst(5500, 6, 1500, 1000)
+LAMPE2: progLampFireBursts(5500, 6, 1000, 600, 4600)
 Ausgabe: Übergang fade 1000 ms, Blinder von 'pause (2)' klingt noch 500 ms aus
-Schluss (22 Beats): progBlack(11000, 25)
-   LAMPE1: progLampFireBurst(11000, 25, 3100, 1000)
-   LAMPE2: progLampFireBurst(11000, 25, 7100, 1000)
+Schluss (22 Beats): progBlack(11000, 7)
+   LAMPE1: progLampFireBurst(11000, 7, 3100, 1000)
+   LAMPE2: progLampFireBurst(11000, 7, 7100, 1000)
    Text (Matrix): "THE NERDS ON": THE 4 x, NERDS 4 x, ON 4 x 1000 ms, ein Durchlauf 12000 ms (über der Szene)
       pulsiert alle 8 Beat(s), Tiefe 100 %, darunter 30 %
-   Ausgabe: Blinder bei 0 ms, 1000 ms lang, Blinder blendet 0 ms ein, 250 ms voll, 750 ms aus, Blinder bei 4000 ms, 1000 ms lang, Blinder blendet 0 ms ein, 250 ms voll, 750 ms aus, Blinder bei 8000 ms, 1000 ms lang, Blinder blendet 0 ms ein, 250 ms voll, 750 ms aus
+   Ausgabe: Blinder bei 0 ms, 1000 ms lang, Blinder blendet 0 ms ein, 250 ms voll, 750 ms aus, Blinder bei 4000 ms, 1000 ms lang, Blinder blendet 0 ms ein, 250 ms voll, 750 ms aus, Blinder bei 8000 ms, 1000 ms lang, Blinder blendet 0 ms ein, 250 ms voll, 750 ms aus, Blinder liegt unter dem Text
 Gitarren dunkel, auf der Matrix laufen die Wasserwellen weiter, auf den Lampen noch fünf Feuer-Impulse im Wechsel (Takt 34,5 bis 40,5). Ab Takt 37 dreimal im Abstand von 2 Takten: Blinder auf allen Geräten und ein Wort weiß auf der Matrix über den Wellen, das jeweils ausblendet - THE, NERDS, ON.</t>
         </is>
       </c>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>progStrobo(1000, 30, 83, getRandomColor(), getRandomColor(), getRandomColor())
+          <t>progStrobo(1000, 8, 83, getRandomColor(), getRandomColor(), getRandomColor())
 Text (Matrix): "FIRE": steht durchgehend, ohne Pulsieren (ausgestanzt aus der Szene)
 Alter Effekt: Strobo in Zufallsfarben auf allen Geräten ('I don't care'); auf der Matrix ist "FIRE" schwarz aus dem Strobo ausgestanzt. Danach ohne Pause in den Chorus von I Love It.</t>
         </is>
